--- a/XBRL-template-MPERS/Company/09-SOCIE.xlsx
+++ b/XBRL-template-MPERS/Company/09-SOCIE.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -446,308 +446,168 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure of changes in equity [abstract]</t>
+          <t>Disclosure of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [abstract]</t>
+          <t>Statement of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement of changes in equity [table]</t>
+          <t>Equity at beginning of period</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Impact of changes in accounting policies</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Equity at beginning of period, restated</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Changes in equity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Components of equity [axis]</t>
+          <t>Comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Equity [member]</t>
+          <t>Profit (loss)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Equity attributable to owners of parent [member]</t>
+          <t>Total other comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Issued capital [member]</t>
-        </is>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>*Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>1*B10+1*B11</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>1*C10+1*C11</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Retained earnings [member]</t>
+          <t>Contributions by and distributions to owners</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Treasury shares [member]</t>
+          <t>Acquisition (dilution) of equity interest in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Reserves [Member]</t>
+          <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sub-total of non-distributable reserves [Member]</t>
+          <t>Dividends paid</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Capital reserve [member]</t>
+          <t>Issuance of shares</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve [member]</t>
+          <t>Issue of convertible notes, net of tax</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Revaluation surplus [member]</t>
+          <t>Increase (decrease) through share-based payment transactions, equity</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Other non-distributable reserves [member]</t>
+          <t>Treasury shares transactions</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Other distributable reserves [member]</t>
+          <t>Other transactions with owners</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Equity, others components [member]</t>
+          <t>Increase (decrease) through other changes, equity</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Non-controlling interests [member]</t>
-        </is>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>*Total increase (decrease) in equity</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>1*B12+1*B14+1*B15+-1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B22</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>1*C12+1*C14+1*C15+-1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C22</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
-        <is>
-          <t>Statement of changes in equity [line items]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Equity at beginning of period</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Impact of changes in accounting policies</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Equity at beginning of period, restated</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Changes in equity [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Comprehensive income [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Profit (loss)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Total other comprehensive income</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>*Total comprehensive income</t>
-        </is>
-      </c>
-      <c r="B32">
-        <f>1*B30+1*B31</f>
-        <v/>
-      </c>
-      <c r="C32">
-        <f>1*C30+1*C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Contributions by and distributions to owners [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Acquisition (dilution) of equity interest in subsidiaries</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Arising from conversion of Irredeemable Convertible Unsecured Loan Stock (ICULS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dividends paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Issuance of shares</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Issue of convertible notes, net of tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Increase (decrease) through share-based payment transactions, equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Treasury shares transactions</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Other transactions with owners</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Increase (decrease) through other changes, equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>*Total increase (decrease) in equity</t>
-        </is>
-      </c>
-      <c r="B43">
-        <f>1*B32+1*B34+1*B35+-1*B36+1*B37+1*B38+1*B39+1*B40+1*B41+1*B42</f>
-        <v/>
-      </c>
-      <c r="C43">
-        <f>1*C32+1*C34+1*C35+-1*C36+1*C37+1*C38+1*C39+1*C40+1*C41+1*C42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
         <is>
           <t>Equity at end of period</t>
         </is>

--- a/XBRL-template-MPERS/Company/09-SOCIE.xlsx
+++ b/XBRL-template-MPERS/Company/09-SOCIE.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +27,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,14 +455,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure of changes in equity</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Statement of changes in equity</t>
         </is>
@@ -479,14 +490,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Changes in equity</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Comprehensive income</t>
         </is>
@@ -507,7 +518,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>*Total comprehensive income</t>
         </is>
@@ -522,7 +533,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Contributions by and distributions to owners</t>
         </is>
@@ -592,7 +603,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>*Total increase (decrease) in equity</t>
         </is>
